--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:54</t>
+    <t xml:space="preserve">2026-10-05 10:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -994,7 +994,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>409760.12</v>
+        <v>409760.13</v>
       </c>
     </row>
     <row r="24">
@@ -1147,7 +1147,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>371511.12</v>
+        <v>371511.13</v>
       </c>
     </row>
     <row r="33">
@@ -1249,7 +1249,7 @@
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>334567.12</v>
+        <v>334567.13</v>
       </c>
     </row>
     <row r="39">
